--- a/backend/data/brands.xlsx
+++ b/backend/data/brands.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-10-05T02:09:42.581266</t>
+          <t>2026-10-11T20:13:03.622285</t>
         </is>
       </c>
     </row>
